--- a/Assets/02Script/Table/ObjectTable.xlsx
+++ b/Assets/02Script/Table/ObjectTable.xlsx
@@ -6,7 +6,6 @@
     <sheet state="visible" name="Pickable" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="Interactable" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="Inspectable" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Readable" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -14,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="53">
   <si>
     <t>ItemID</t>
   </si>
@@ -37,44 +36,84 @@
     <t>PairID</t>
   </si>
   <si>
-    <t>흙 묻은 열쇠</t>
+    <t>오래된 초콜릿</t>
   </si>
   <si>
     <t>Pickable</t>
   </si>
   <si>
-    <t>바닥에 떨어져 있는 흙이 많이 묻은&lt;b&gt;열쇠&lt;/b&gt;.</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;흙 묻은 열쇠&lt;/color&gt;를 주웠다.</t>
-  </si>
-  <si>
-    <t>Icon_0</t>
+    <t>바닥에 떨어져 있던 오래돼 보이는 초콜릿.
+유통기한이....언제 까지지?</t>
+  </si>
+  <si>
+    <t>더러운 초콜릿을 주웠다.</t>
+  </si>
+  <si>
+    <t>Icon_1</t>
+  </si>
+  <si>
+    <t>오래된 나무 열쇠 손잡이</t>
+  </si>
+  <si>
+    <t>얼마나 오래됐는지 가늠이 가질 않는다.
+아까 봤던 문의 열쇠인가?</t>
+  </si>
+  <si>
+    <t>오래된 나무 열쇠의 손잡이를 주웠다.</t>
+  </si>
+  <si>
+    <t>Icon_2</t>
   </si>
   <si>
     <t>P001</t>
   </si>
   <si>
-    <t>오래된 초콜릿</t>
-  </si>
-  <si>
-    <t>바닥에 떨어져 있던 오래돼 보이는 초콜릿.
-먹지 않는게 좋을 것 같다.</t>
-  </si>
-  <si>
-    <t>더러운 초콜릿을 주웠다.</t>
-  </si>
-  <si>
-    <t>Icon_1</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>DeactiveMSG</t>
+    <t>오래된 나무 열쇠 중간부분</t>
+  </si>
+  <si>
+    <t>오래된 나무 열쇠의 중간 부분을 주웠다.</t>
+  </si>
+  <si>
+    <t>Icon_3</t>
+  </si>
+  <si>
+    <t>Icon_4</t>
+  </si>
+  <si>
+    <t>오래된 나무 열쇠 끝부분</t>
+  </si>
+  <si>
+    <t>오래된 나무 열쇠의 끝부분을 주웠다.</t>
+  </si>
+  <si>
+    <t>Icon_5</t>
+  </si>
+  <si>
+    <t>하얀 실</t>
+  </si>
+  <si>
+    <t>이건... 어디에 쓰는거지?</t>
+  </si>
+  <si>
+    <t>하얀색의 실을 주웠다.</t>
+  </si>
+  <si>
+    <t>Icon_6</t>
+  </si>
+  <si>
+    <t>P002</t>
+  </si>
+  <si>
+    <t>Monologue</t>
+  </si>
+  <si>
+    <t>ActiveMSG</t>
   </si>
   <si>
     <t>RejectMSG</t>
+  </si>
+  <si>
+    <t>HNum</t>
   </si>
   <si>
     <t>오래돼 보이는 나무 문</t>
@@ -87,59 +126,63 @@
 &lt;i&gt;작게 열쇠구멍이 보인다.&lt;/i&gt;</t>
   </si>
   <si>
+    <t>열래말래</t>
+  </si>
+  <si>
     <t>안열래요</t>
   </si>
   <si>
-    <t>Monologue</t>
-  </si>
-  <si>
-    <t>흔한 바위</t>
+    <t>날카로운 바늘</t>
+  </si>
+  <si>
+    <t>날카로운 바늘이다.
+&lt;i&gt;바늘구멍이 유난히 큰 것 같기도...?&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>실을 바늘구멍에 끼워볼까요~?</t>
+  </si>
+  <si>
+    <t>그만뒀다.</t>
+  </si>
+  <si>
+    <t>덤불</t>
   </si>
   <si>
     <t>Inspectable</t>
   </si>
   <si>
-    <t>흔한 &lt;color=blue&gt;바위&lt;/color&gt;다.
+    <t>깔끔하게 정돈된&lt;color=blue&gt;덤불&lt;/color&gt;다.
 &lt;i&gt;어, 자세히 보니......&lt;/i&gt;
-자세히 봐도 그냥&lt;b&gt;바위&lt;/b&gt;다.</t>
-  </si>
-  <si>
-    <t>노란색 꽃</t>
-  </si>
-  <si>
-    <t>은은하게 노란빛을 띄고 있는 &lt;b&gt;꽃&lt;/b&gt;이다.
-향기가 좋은 것 같다.</t>
-  </si>
-  <si>
-    <t>하얀색 꽃</t>
-  </si>
-  <si>
-    <t>하얗고 이쁘게 피어있는 &lt;b&gt;꽃&lt;/b&gt;이다.
-&lt;i&gt;그러고 보니...&lt;/i&gt;
-난 노란색보단 하얀색을 더 좋아했던 것 같다.</t>
+&lt;b&gt;애벌레&lt;/b&gt;가 기어다니고 있다.</t>
   </si>
   <si>
     <t>커다란 나무</t>
   </si>
   <si>
-    <t>Narrative</t>
-  </si>
-  <si>
-    <t>찢어진 신문지</t>
-  </si>
-  <si>
-    <t>Readable</t>
-  </si>
-  <si>
-    <t>바닥에 버려져있는 &lt;color=red&gt;찢어진 신문지&lt;/color&gt;다.
-&lt;b&gt;한번 읽어 볼까?&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;이 편지는 영국에서 최초로 시작되어...&lt;/b&gt; 일 년에 한 바퀴를 돌면서 받는 사람에게 행운을 주었고 지금은 당신에게로 옮겨진 이 편지는 4일 안에 당신 곁을 떠나야 합니다. 이 편지를 포함해서 7통을 행운이 필요한 사람에게 보내 주셔야 합니다. 복사를 해도 좋습니다. 혹 미신이라 하실지 모르지만 사실입니다.
-영국에서 HGXWCH이라는 사람은 1930년에 이 편지를 받았습니다. 그는 비서에게 복사해서 보내라고 했습니다. 며칠 뒤에 복권이 당첨되어 20억을 받았습니다. 어떤 이는 이 편지를 받았으나 96시간 이내 자신의 손에서 떠나야 한다는 사실을 잊었습니다. 그는 곧 사직되었습니다. 나중에야 이 사실을 알고 7통의 편지를 보냈는데 다시 좋은 직장을 얻었습니다. 미국의 케네디 대통령은 이 편지를 받았지만 그냥 버렸습니다. 결국 9일 후 그는 암살당했습니다. 기억해 주세요. 이 편지를 보내면 7년의 행운이 있을 것이고 그렇지 않으면 3년의 불행이 있을 것입니다. 그리고 이 편지를 버리거나 낙서를 해서는 절대로 안됩니다. 7통입니다. 이 편지를 받은 사람은 행운이 깃들 것입니다. 힘들겠지만 좋은 게 좋다고 생각하세요. 7년의 행운을 빌면서...</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;...................?&lt;/i&gt;</t>
+    <t>올려다보기 힘들 정도로 &lt;b&gt;커다란 나무&lt;/b&gt;다.
+얼마나 오래 산 걸까?</t>
+  </si>
+  <si>
+    <t>벚꽃 나무</t>
+  </si>
+  <si>
+    <t>핑크빛 꽃을 아름답게 피운&lt;b&gt;벚꽃 나무&lt;/b&gt;다.
+&lt;i&gt;어, 그러고보니...&lt;/i&gt;
+지금이 봄이던가..?</t>
+  </si>
+  <si>
+    <t>분수대</t>
+  </si>
+  <si>
+    <t>아름답게 조형되어 눈이 부시는&lt;b&gt;분수대&lt;/b&gt;다.
+보는 것만으로도 시원한 느낌이다.</t>
+  </si>
+  <si>
+    <t>공중에 떠있는 풍선</t>
+  </si>
+  <si>
+    <t>어린시절 손에 쥐고있던 풍선인 것 같다.
+그땐.. 행복했는데..</t>
   </si>
 </sst>
 </file>
@@ -204,10 +247,6 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -412,10 +451,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="18.75"/>
+    <col customWidth="1" min="2" max="2" width="22.38"/>
     <col customWidth="1" min="3" max="3" width="18.5"/>
-    <col customWidth="1" min="4" max="4" width="36.13"/>
+    <col customWidth="1" min="4" max="4" width="37.38"/>
     <col customWidth="1" min="5" max="5" width="33.5"/>
+    <col customWidth="1" min="6" max="6" width="21.0"/>
+    <col customWidth="1" min="7" max="7" width="27.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,31 +501,120 @@
       <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
         <v>1.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="1" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>1.0001003E7</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>1.0001004E7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>1.0001005E7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>1.0001006E7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -501,8 +631,8 @@
   <cols>
     <col customWidth="1" min="2" max="2" width="17.38"/>
     <col customWidth="1" min="4" max="4" width="47.75"/>
-    <col customWidth="1" min="5" max="5" width="25.38"/>
-    <col customWidth="1" min="6" max="6" width="14.25"/>
+    <col customWidth="1" min="5" max="6" width="25.38"/>
+    <col customWidth="1" min="7" max="7" width="14.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,13 +646,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -530,19 +666,51 @@
         <v>2.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2.0001002E7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -557,7 +725,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="34.5"/>
+    <col customWidth="1" min="2" max="2" width="14.25"/>
+    <col customWidth="1" min="4" max="4" width="41.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -571,7 +740,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -579,27 +748,27 @@
         <v>3.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" ht="38.25" customHeight="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1">
         <v>3.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" ht="37.5" customHeight="1">
@@ -607,85 +776,48 @@
         <v>3.0001003E7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" ht="39.0" customHeight="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1">
         <v>3.0001004E7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="4" max="4" width="33.5"/>
-    <col customWidth="1" min="5" max="5" width="130.25"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1">
-        <v>4.0001001E7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" ht="36.75" customHeight="1">
+      <c r="A6" s="1">
+        <v>3.0001005E7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" ht="33.75" customHeight="1"/>
+    <row r="8" ht="33.0" customHeight="1"/>
+    <row r="9" ht="46.5" customHeight="1"/>
+    <row r="10" ht="51.75" customHeight="1"/>
+    <row r="11" ht="54.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Assets/02Script/Table/ObjectTable.xlsx
+++ b/Assets/02Script/Table/ObjectTable.xlsx
@@ -4,8 +4,9 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Pickable" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Interactable" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Inspectable" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Eatable" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Interactable" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Inspectable" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -13,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="60">
   <si>
     <t>ItemID</t>
   </si>
@@ -49,7 +50,7 @@
     <t>더러운 초콜릿을 주웠다.</t>
   </si>
   <si>
-    <t>Icon_1</t>
+    <t>Icon_P1</t>
   </si>
   <si>
     <t>오래된 나무 열쇠 손잡이</t>
@@ -62,7 +63,7 @@
     <t>오래된 나무 열쇠의 손잡이를 주웠다.</t>
   </si>
   <si>
-    <t>Icon_2</t>
+    <t>Icon_P2</t>
   </si>
   <si>
     <t>P001</t>
@@ -74,10 +75,10 @@
     <t>오래된 나무 열쇠의 중간 부분을 주웠다.</t>
   </si>
   <si>
-    <t>Icon_3</t>
-  </si>
-  <si>
-    <t>Icon_4</t>
+    <t>Icon_P3</t>
+  </si>
+  <si>
+    <t>Icon_P4</t>
   </si>
   <si>
     <t>오래된 나무 열쇠 끝부분</t>
@@ -86,7 +87,7 @@
     <t>오래된 나무 열쇠의 끝부분을 주웠다.</t>
   </si>
   <si>
-    <t>Icon_5</t>
+    <t>Icon_P5</t>
   </si>
   <si>
     <t>하얀 실</t>
@@ -98,10 +99,32 @@
     <t>하얀색의 실을 주웠다.</t>
   </si>
   <si>
-    <t>Icon_6</t>
+    <t>Icon_P6</t>
   </si>
   <si>
     <t>P002</t>
+  </si>
+  <si>
+    <t>Mental</t>
+  </si>
+  <si>
+    <t>Eatable</t>
+  </si>
+  <si>
+    <t>Icon_E1</t>
+  </si>
+  <si>
+    <t>홍삼 캔디</t>
+  </si>
+  <si>
+    <t>홍삼 농축액 25%가 함유된 고급스러운 캔디.
+엄청 쓸거같다.</t>
+  </si>
+  <si>
+    <t>홍삼 캔디를 주웠다.</t>
+  </si>
+  <si>
+    <t>Icon_E2</t>
   </si>
   <si>
     <t>Monologue</t>
@@ -247,6 +270,10 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -594,7 +621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="30.0" customHeight="1">
       <c r="A7" s="1">
         <v>1.0001006E7</v>
       </c>
@@ -623,6 +650,95 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="17.75"/>
+    <col customWidth="1" min="2" max="2" width="19.88"/>
+    <col customWidth="1" min="3" max="3" width="20.38"/>
+    <col customWidth="1" min="4" max="4" width="29.0"/>
+    <col customWidth="1" min="5" max="5" width="23.88"/>
+    <col customWidth="1" min="6" max="6" width="18.25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>2.0001001E7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1">
+        <v>-10.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2.0001002E7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="1">
+        <v>10.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -646,39 +762,39 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>2.0001001E7</v>
+        <v>3.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -689,22 +805,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>2.0001002E7</v>
+        <v>3.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>28</v>
@@ -718,7 +834,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -740,77 +856,77 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>3.0001001E7</v>
+        <v>4.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>3.0001002E7</v>
+        <v>4.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" ht="37.5" customHeight="1">
       <c r="A4" s="1">
-        <v>3.0001003E7</v>
+        <v>4.0001003E7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>3.0001004E7</v>
+        <v>4.0001004E7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" ht="36.75" customHeight="1">
       <c r="A6" s="1">
-        <v>3.0001005E7</v>
+        <v>4.0001005E7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" ht="33.75" customHeight="1"/>

--- a/Assets/02Script/Table/ObjectTable.xlsx
+++ b/Assets/02Script/Table/ObjectTable.xlsx
@@ -145,7 +145,7 @@
     <t>Interactable</t>
   </si>
   <si>
-    <t>&lt;color=green&gt;열쇠가 있어야 열 수 있는 문&lt;/color&gt;이다.
+    <t>열쇠가 있어야 열 수 있는 문이다.
 &lt;i&gt;작게 열쇠구멍이 보인다.&lt;/i&gt;</t>
   </si>
   <si>
@@ -174,22 +174,22 @@
     <t>Inspectable</t>
   </si>
   <si>
-    <t>깔끔하게 정돈된&lt;color=blue&gt;덤불&lt;/color&gt;다.
+    <t>깔끔하게 정돈 된 덤불이다.
 &lt;i&gt;어, 자세히 보니......&lt;/i&gt;
-&lt;b&gt;애벌레&lt;/b&gt;가 기어다니고 있다.</t>
+애벌레가 기어다니고 있다.</t>
   </si>
   <si>
     <t>커다란 나무</t>
   </si>
   <si>
-    <t>올려다보기 힘들 정도로 &lt;b&gt;커다란 나무&lt;/b&gt;다.
+    <t>올려다보기 힘들 정도로 커다란 나무다.
 얼마나 오래 산 걸까?</t>
   </si>
   <si>
     <t>벚꽃 나무</t>
   </si>
   <si>
-    <t>핑크빛 꽃을 아름답게 피운&lt;b&gt;벚꽃 나무&lt;/b&gt;다.
+    <t>핑크빛 꽃을 아름답게 피운 벚꽃 나무다.
 &lt;i&gt;어, 그러고보니...&lt;/i&gt;
 지금이 봄이던가..?</t>
   </si>
@@ -197,7 +197,7 @@
     <t>분수대</t>
   </si>
   <si>
-    <t>아름답게 조형되어 눈이 부시는&lt;b&gt;분수대&lt;/b&gt;다.
+    <t>아름답게 조형되어 눈이 부시는 분수대다.
 보는 것만으로도 시원한 느낌이다.</t>
   </si>
   <si>

--- a/Assets/02Script/Table/ObjectTable.xlsx
+++ b/Assets/02Script/Table/ObjectTable.xlsx
@@ -7,6 +7,7 @@
     <sheet state="visible" name="Eatable" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="Interactable" sheetId="3" r:id="rId6"/>
     <sheet state="visible" name="Inspectable" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="Note" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="70">
   <si>
     <t>ItemID</t>
   </si>
@@ -35,6 +36,9 @@
   </si>
   <si>
     <t>PairID</t>
+  </si>
+  <si>
+    <t>Subsist</t>
   </si>
   <si>
     <t>오래된 초콜릿</t>
@@ -60,7 +64,7 @@
 아까 봤던 문의 열쇠인가?</t>
   </si>
   <si>
-    <t>오래된 나무 열쇠의 손잡이를 주웠다.</t>
+    <t>오래된 나무 열쇠의 손잡이를 받았다.</t>
   </si>
   <si>
     <t>Icon_P2</t>
@@ -72,7 +76,7 @@
     <t>오래된 나무 열쇠 중간부분</t>
   </si>
   <si>
-    <t>오래된 나무 열쇠의 중간 부분을 주웠다.</t>
+    <t>오래된 나무 열쇠의 중간 부분을 받았다.</t>
   </si>
   <si>
     <t>Icon_P3</t>
@@ -81,7 +85,7 @@
     <t>오래된 나무 열쇠 끝부분</t>
   </si>
   <si>
-    <t>오래된 나무 열쇠의 끝부분을 주웠다.</t>
+    <t>오래된 나무 열쇠의 끝부분을 받았다.</t>
   </si>
   <si>
     <t>Icon_P4</t>
@@ -93,13 +97,41 @@
     <t>이건... 어디에 쓰는거지?</t>
   </si>
   <si>
-    <t>하얀색의 실을 주웠다.</t>
+    <t>하얀색 실을 주웠다.</t>
   </si>
   <si>
     <t>Icon_P5</t>
   </si>
   <si>
     <t>P002</t>
+  </si>
+  <si>
+    <t>먼지 묻은 종이조각</t>
+  </si>
+  <si>
+    <t>흙과 먼지가 잔뜩 묻어있는 찢어진 종이 조각.
+.........ㅇ....쳐.... 
+뭐라고 적혀있는지 알아보기 힘들다.</t>
+  </si>
+  <si>
+    <t>찢어진 종이 조각을 주웠다.</t>
+  </si>
+  <si>
+    <t>Icon_P6</t>
+  </si>
+  <si>
+    <t>오래된 사진 조각</t>
+  </si>
+  <si>
+    <t>언제 찍은지 모를 낡은 사진.
+누구일까?
+어딘지 모르게 낯이 익다.</t>
+  </si>
+  <si>
+    <t>오래된 사진을 주웠다.</t>
+  </si>
+  <si>
+    <t>Icon_P7</t>
   </si>
   <si>
     <t>Mental</t>
@@ -165,25 +197,10 @@
     <t>그만뒀다.</t>
   </si>
   <si>
-    <t>덤불</t>
+    <t>벚꽃 나무</t>
   </si>
   <si>
     <t>Inspectable</t>
-  </si>
-  <si>
-    <t>깔끔하게 정돈 된 덤불이다.
-&lt;i&gt;어, 자세히 보니......&lt;/i&gt;
-애벌레가 기어다니고 있다.</t>
-  </si>
-  <si>
-    <t>커다란 나무</t>
-  </si>
-  <si>
-    <t>올려다보기 힘들 정도로 커다란 나무다.
-얼마나 오래 산 걸까?</t>
-  </si>
-  <si>
-    <t>벚꽃 나무</t>
   </si>
   <si>
     <t>핑크빛 꽃을 아름답게 피운 벚꽃 나무다.
@@ -198,11 +215,31 @@
 보는 것만으로도 시원한 느낌이다.</t>
   </si>
   <si>
-    <t>공중에 떠있는 풍선</t>
-  </si>
-  <si>
-    <t>어린시절 손에 쥐고있던 풍선인 것 같다.
-그땐.. 행복했는데..</t>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>룰쪽지1</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>꿈속임을 인지하지마라</t>
+  </si>
+  <si>
+    <t>찢어진 메모를 주웠다.
+중요한 내용 같으니 주워놔볼까...</t>
+  </si>
+  <si>
+    <t>룰쪽지2</t>
+  </si>
+  <si>
+    <t>살고싶다는 마음을 가지고 뛰어라</t>
+  </si>
+  <si>
+    <t>찢어진 메모를 주웠다.
+찢어진 모양이 익숙한 것 같은데.
+아, 혹시...?</t>
   </si>
 </sst>
 </file>
@@ -240,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -250,6 +287,12 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -271,6 +314,10 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -480,7 +527,7 @@
     <col customWidth="1" min="4" max="4" width="37.38"/>
     <col customWidth="1" min="5" max="5" width="33.5"/>
     <col customWidth="1" min="6" max="6" width="21.0"/>
-    <col customWidth="1" min="7" max="7" width="27.63"/>
+    <col customWidth="1" min="7" max="7" width="15.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,25 +552,31 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>1.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="3">
@@ -531,22 +584,25 @@
         <v>1.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -554,22 +610,25 @@
         <v>1.0001003E7</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>16</v>
+      <c r="H4" s="1">
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -577,22 +636,25 @@
         <v>1.0001004E7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.0</v>
       </c>
     </row>
     <row r="6" ht="30.0" customHeight="1">
@@ -600,22 +662,65 @@
         <v>1.0001005E7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>1.0001006E7</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>1.0001007E7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -658,7 +763,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
@@ -666,19 +771,19 @@
         <v>2.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G2" s="1">
         <v>-10.0</v>
@@ -689,19 +794,19 @@
         <v>2.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G3" s="1">
         <v>10.0</v>
@@ -736,19 +841,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
@@ -756,22 +861,22 @@
         <v>3.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="1">
         <v>4.0</v>
@@ -782,22 +887,22 @@
         <v>3.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" s="1">
         <v>1.0</v>
@@ -830,7 +935,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
@@ -838,13 +943,13 @@
         <v>4.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
@@ -852,57 +957,17 @@
         <v>4.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" ht="37.5" customHeight="1">
-      <c r="A4" s="1">
-        <v>4.0001003E7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1">
-        <v>4.0001004E7</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" ht="36.75" customHeight="1">
-      <c r="A6" s="1">
-        <v>4.0001005E7</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" ht="37.5" customHeight="1"/>
+    <row r="6" ht="36.75" customHeight="1"/>
     <row r="7" ht="33.75" customHeight="1"/>
     <row r="8" ht="33.0" customHeight="1"/>
     <row r="9" ht="46.5" customHeight="1"/>
@@ -911,4 +976,71 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="4" max="4" width="32.38"/>
+    <col customWidth="1" min="5" max="5" width="27.25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>5.0001001E7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>5.0001002E7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Assets/02Script/Table/ObjectTable.xlsx
+++ b/Assets/02Script/Table/ObjectTable.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="75">
   <si>
     <t>ItemID</t>
   </si>
@@ -156,6 +156,15 @@
     <t>Icon_E2</t>
   </si>
   <si>
+    <t>임시</t>
+  </si>
+  <si>
+    <t>먹으면 죽어요</t>
+  </si>
+  <si>
+    <t>Icon_E3</t>
+  </si>
+  <si>
     <t>Monologue</t>
   </si>
   <si>
@@ -215,6 +224,13 @@
 보는 것만으로도 시원한 느낌이다.</t>
   </si>
   <si>
+    <t>서린이 방 문</t>
+  </si>
+  <si>
+    <t>밖에 나가기엔 늦은 시간이야..
+내일을 위해서 어서 자야 해.</t>
+  </si>
+  <si>
     <t>Text</t>
   </si>
   <si>
@@ -228,6 +244,7 @@
   </si>
   <si>
     <t>찢어진 메모를 주웠다.
+꿈의 규칙...?
 중요한 내용 같으니 주워놔볼까...</t>
   </si>
   <si>
@@ -263,12 +280,18 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
+        <bgColor rgb="FFF6F8F9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -277,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -289,6 +312,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -812,6 +838,29 @@
         <v>10.0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>2.0001003E7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="1">
+        <v>-100.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -841,19 +890,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
@@ -861,19 +910,19 @@
         <v>3.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -887,19 +936,19 @@
         <v>3.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>28</v>
@@ -935,7 +984,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
@@ -943,13 +992,13 @@
         <v>4.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
@@ -957,16 +1006,29 @@
         <v>4.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" ht="37.5" customHeight="1">
+      <c r="A4" s="1">
+        <v>4.0001003E7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="4" ht="37.5" customHeight="1"/>
+      <c r="D4" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
     <row r="6" ht="36.75" customHeight="1"/>
     <row r="7" ht="33.75" customHeight="1"/>
     <row r="8" ht="33.0" customHeight="1"/>
@@ -999,8 +1061,8 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>62</v>
+      <c r="D1" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -1011,16 +1073,16 @@
         <v>5.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -1028,16 +1090,16 @@
         <v>5.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02Script/Table/ObjectTable.xlsx
+++ b/Assets/02Script/Table/ObjectTable.xlsx
@@ -3,11 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Pickable" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Eatable" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Interactable" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Inspectable" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="Note" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="Pickable" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Eatable" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Interactable" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Inspectable" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Note" sheetId="5" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="77">
   <si>
     <t>ItemID</t>
   </si>
@@ -229,6 +229,13 @@
   <si>
     <t>밖에 나가기엔 늦은 시간이야..
 내일을 위해서 어서 자야 해.</t>
+  </si>
+  <si>
+    <t>자판기</t>
+  </si>
+  <si>
+    <t>자판기를 사용하려면 동전이 필요한데...
+어딘가에서 동전을 얻을 수 있지 않을까..?</t>
   </si>
   <si>
     <t>Text</t>
@@ -345,6 +352,10 @@
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -548,12 +559,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="22.38"/>
-    <col customWidth="1" min="3" max="3" width="18.5"/>
-    <col customWidth="1" min="4" max="4" width="37.38"/>
-    <col customWidth="1" min="5" max="5" width="33.5"/>
-    <col customWidth="1" min="6" max="6" width="21.0"/>
-    <col customWidth="1" min="7" max="7" width="15.88"/>
+    <col customWidth="1" min="2" max="2" width="16.0"/>
+    <col customWidth="1" min="3" max="3" width="9.5"/>
+    <col customWidth="1" min="4" max="4" width="20.63"/>
+    <col customWidth="1" min="5" max="5" width="15.88"/>
+    <col customWidth="1" min="6" max="6" width="9.75"/>
+    <col customWidth="1" min="7" max="7" width="8.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1029,6 +1040,20 @@
         <v>66</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>4.0001004E7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
     <row r="6" ht="36.75" customHeight="1"/>
     <row r="7" ht="33.75" customHeight="1"/>
     <row r="8" ht="33.0" customHeight="1"/>
@@ -1062,7 +1087,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -1073,16 +1098,16 @@
         <v>5.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -1090,16 +1115,16 @@
         <v>5.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
